--- a/www/download/COUNTRY.POL.rpA2.xlsx
+++ b/www/download/COUNTRY.POL.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>Polônia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>2.42412495735975</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>2.69164505131081</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>3.26679958645285</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3.47270458662722</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>3.95882797122747</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>4.33914775167024</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>4.09198792933865</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>4.07830354787578</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>3.88742031091487</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>3.6387453558442</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>3.23185325766701</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>3.10019827648708</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2.75793607453417</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2.37751058134273</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.09692432732096</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14.735</t>
+          <t>2.12436906007462</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.021</t>
+          <t>2.01804160187305</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>15.439</t>
+          <t>1.95393024979135</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>1.93524652652714</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15.375</t>
+          <t>2.20502067557987</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.018</t>
+          <t>2.34707890970289</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>14.195</t>
+          <t>3.05333495924963</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.766</t>
+          <t>3.08474122561262</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>13.606</t>
+          <t>3.58873593283774</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13.773</t>
+          <t>3.55797968001937</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>14.075</t>
+          <t>3.4419077537589</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>3.60138696038919</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>15.174</t>
+          <t>3.5994115681264</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>15.784</t>
+          <t>3.53556045521393</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>15.786</t>
+          <t>4.01817147716665</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.714</t>
+          <t>1.33679174153848</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.725</t>
+          <t>1.21163205994336</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.863</t>
+          <t>1.16789682215832</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8.938</t>
+          <t>1.122165468216</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.896</t>
+          <t>1.3176399045609</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.354</t>
+          <t>1.45856553666199</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10.207</t>
+          <t>2.09667724171296</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>2.18342487044159</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>9.891</t>
+          <t>2.2836621244041</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>10.084</t>
+          <t>2.52222505588563</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.436</t>
+          <t>2.39172317922458</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>10.963</t>
+          <t>2.49963589399246</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>11.605</t>
+          <t>2.56559593717258</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>12.126</t>
+          <t>2.33867334952557</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>12.207</t>
+          <t>2.58943029978565</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>28305.086</t>
+          <t>0.19730413652878</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>28879.294</t>
+          <t>0.155239799849046</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29662.441</t>
+          <t>0.146954615800317</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>30129.465</t>
+          <t>0.109792134504211</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29829.818</t>
+          <t>0.201648486288729</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>28892.502</t>
+          <t>0.311766135431639</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26456.571</t>
+          <t>0.634733867706555</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>25507.399</t>
+          <t>0.689712891540164</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>25162.379</t>
+          <t>0.201491695934551</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>25538.377</t>
+          <t>0.873805870148205</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>25769.666</t>
+          <t>0.781719080124688</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26509.432</t>
+          <t>0.841891097688142</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>27585.81</t>
+          <t>0.914162527370593</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>28604.274</t>
+          <t>0.72613232866129</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>28297.15</t>
+          <t>0.842825977449665</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15014.242</t>
+          <t>90003533031.5729</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15032.708</t>
+          <t>91394582124.9977</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15287.945</t>
+          <t>89535309364.7072</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>15407.358</t>
+          <t>89322299948.5099</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>15801.55</t>
+          <t>85825928243.9657</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16365.614</t>
+          <t>86590829196.2869</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>17542.312</t>
+          <t>78209769355.1684</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16854.515</t>
+          <t>74845286249.5308</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>16906.382</t>
+          <t>76377218739.4546</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17319.251</t>
+          <t>79770075204.6413</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>17709.691</t>
+          <t>83329891971.7114</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>18612.378</t>
+          <t>87622268825.6431</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>19705.785</t>
+          <t>93473530934.7986</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20418.937</t>
+          <t>93528830483.6832</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>20070.824</t>
+          <t>87265670860.7326</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>17871135849.4213</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18798201417.9995</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>19512216965.9773</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>20064186355.3467</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18908855536.3586</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>18493580435.3753</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>16058080176.7667</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>15299251920.6358</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>15066994122.9634</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>14681148149.7548</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>15720567781.1179</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>16079974695.5454</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>16839022086.4845</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>18321296947.4581</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>16872353022.5671</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>10632078.0386781</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>9756897.42845429</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>9692043.30482081</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>9063343.07488521</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>9426593.73621722</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>9004144.38841259</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>71.37</t>
+          <t>7820402.26779621</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>7227306.02301919</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>6587552.08547725</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>67.04</t>
+          <t>5649886.39057701</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>66.25</t>
+          <t>5096465.44329546</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>4658073.50969081</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>64.7</t>
+          <t>3951298.82745926</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>64.93</t>
+          <t>3158637.05146223</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>3809980.52484177</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>225134.338189787</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>227089.060881696</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>225088.729574429</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>222164.320830219</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>221911.150575807</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>217734.487049145</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>190797.762105857</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>187364.612185869</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>203975.162751136</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>226873.058242662</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>248440.230968451</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>267635.112178856</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>308076.43422059</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>351802.856120461</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.93</t>
+          <t>322752.818845542</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>392608.851160413</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>397459.334604282</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>382954.752902019</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>377334.758020929</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>374072.308083116</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24.56</t>
+          <t>379558.90106727</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>26.55</t>
+          <t>330705.022025713</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>320547.064502152</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>350221.18143249</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>396724.745185446</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>440813.239788276</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>482425.04802816</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>36.83</t>
+          <t>576930.760792721</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>630612.041704561</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>543844.089307807</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>1.46282514272786</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>1.3476835532343</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>1.30408588839403</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>1.26600748654529</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>1.4792574453321</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>1.62244688365071</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>69.63</t>
+          <t>2.28427091603045</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>68.54</t>
+          <t>2.38567804340551</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>66.43</t>
+          <t>2.5534432876216</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>63.6</t>
+          <t>2.83102409033624</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>62.33</t>
+          <t>2.72898541730878</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>61.43</t>
+          <t>2.86589320428112</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>60.72</t>
+          <t>2.91289752911254</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>60.07</t>
+          <t>2.73712046981538</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>3.11292797932591</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>32576.0339670849</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>36808.2738750884</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>39096.1452575262</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>42666.8431366874</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>43137.6454940369</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>44093.3977422624</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>46807.1881066426</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>49867.4481896885</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>55784.322017333</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>63773.1867390281</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>72651.060032066</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>78521.8156547962</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>95388.6672297573</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2.42412495735975</t>
+          <t>2050.92393006659</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.69164505131081</t>
+          <t>2154.59573601378</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.26679958645285</t>
+          <t>2201.48670525062</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.47270458662722</t>
+          <t>2244.71788634954</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.95882797122747</t>
+          <t>2125.54581119139</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.33914775167024</t>
+          <t>1977.05609683191</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.09198792933865</t>
+          <t>1573.30356600305</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.07830354787578</t>
+          <t>1548.58564913566</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.88742031091487</t>
+          <t>1523.33422200059</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.6387453558442</t>
+          <t>1455.91425353089</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3.23185325766701</t>
+          <t>1506.33536608931</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3.10019827648708</t>
+          <t>1466.76287255611</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.75793607453417</t>
+          <t>1451.02690126451</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.37751058134273</t>
+          <t>1510.93510922645</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>3.09692432732096</t>
+          <t>1382.22066754873</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>-4063341745.46736</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>-3547438547.02392</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>-4604467856.73461</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>-3462081945.14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-3170759880.86968</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>-2601376282.35188</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>-1944904048.82476</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>-1283849669.2352</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>-1611614529.85755</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>-903261101.994774</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>733496744.339476</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>1037551512.43941</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>2129298088.57042</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>4277265654.10178</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>3897763366.86798</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>-3888709390.78071</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>-3625605098.5744</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>-5030598271.00225</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>-4200430532.58346</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>-3188063756.55098</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-2545799457.30738</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>-1537733328.67393</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>-766713812.572527</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>-1085402637.75519</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>-399379086.941228</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>1268320582.49432</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1600893866.50701</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>2313545999.10469</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>4641607404.36802</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>4008142171.53865</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.427</t>
+          <t>-174632354.686653</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>78166551.5504821</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>426130414.267637</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>738348587.443461</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>17303875.6812968</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>-55576825.0445</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-407170720.15083</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>-517135856.662669</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>-526211892.102358</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>-503882015.053547</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>-534823838.154846</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>-563342354.067605</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>1.043</t>
+          <t>-184247910.534272</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-364341750.266239</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-110378804.670676</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>5051.06702079023</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>5058.30897330832</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>5072.41445105503</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>5086.54753565018</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>5269.77527779072</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>5184.72459993946</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>5167.15514391081</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>5243.01243061148</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>5413.08176597227</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>5577.64257874075</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>5617.10261372353</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>5670.34862130651</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.884</t>
+          <t>5677.71957663372</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.111</t>
+          <t>5646.54652525291</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>5684.97405716372</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>5024.85436492086</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>5019.86826054485</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>5037.42483070371</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>5034.94929742422</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>5157.720423311</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>5097.59007316637</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>5149.49463425661</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>5236.47694087171</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>5406.8095079745</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>5571.011628413</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>5615.99844542579</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>5679.02614880925</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>5704.34584126665</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>5717.17218172152</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>5823.77856139973</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>212.44</t>
+          <t>32273.0904982147</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>201.8</t>
+          <t>34981.3289632228</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>195.39</t>
+          <t>36927.2736772823</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>193.52</t>
+          <t>44720.5519158438</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>40164.013906437</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>234.71</t>
+          <t>46634.020946017</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>305.33</t>
+          <t>51317.5554726516</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>308.47</t>
+          <t>55901.6892476891</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>358.87</t>
+          <t>71127.0532923045</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>355.8</t>
+          <t>93780.533903888</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>344.19</t>
+          <t>112144.879107038</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>360.14</t>
+          <t>137120.586339317</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>359.94</t>
+          <t>174806.150409671</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>353.56</t>
+          <t>213238.291851392</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>401.82</t>
+          <t>165890.059090342</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>133.68</t>
+          <t>12525574286.0314</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>121.16</t>
+          <t>12092681802.5866</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>116.79</t>
+          <t>12395137757.9726</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>112.22</t>
+          <t>13417385384.4477</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>131.76</t>
+          <t>12374189837.4131</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>145.86</t>
+          <t>13111291235.5337</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>209.67</t>
+          <t>13212391025.4888</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>218.34</t>
+          <t>13393595378.6104</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>228.37</t>
+          <t>15255886713.7669</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>252.22</t>
+          <t>17598985787.8083</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>239.17</t>
+          <t>18935654389.4141</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>249.96</t>
+          <t>20992606907.7143</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>256.56</t>
+          <t>22458193877.1057</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>233.87</t>
+          <t>21953659421.9667</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>258.94</t>
+          <t>20544146933.407</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>27947.9236956013</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>35401.5459044805</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>40806.6375670446</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>50367.1160082573</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>47847.6881637181</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>55163.6032673991</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>55959.0223500399</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>68.97</t>
+          <t>60262.9530736781</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>73868.5240165445</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>95764.783608164</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>78.17</t>
+          <t>109753.160494378</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>137410.611722296</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>179302.879672821</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>225277.374472069</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>158895.392346397</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>74042.234</t>
+          <t>7218412148.79825</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>75401.433</t>
+          <t>8663517246.90907</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77771.291</t>
+          <t>8806231117.21869</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>79554.213</t>
+          <t>11528458508.533</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>79299.952</t>
+          <t>11426548138.7619</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>76553.059</t>
+          <t>13031473866.6278</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>73096.046</t>
+          <t>12721153596.8899</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>72086.913</t>
+          <t>13473256169.9651</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>73565.591</t>
+          <t>14456001203.402</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>76731.214</t>
+          <t>17240454571.1292</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>79042.37</t>
+          <t>19057631573.343</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>82515.682</t>
+          <t>22098309036.9686</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>86558.885</t>
+          <t>25525585753.9199</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>90237.821</t>
+          <t>28502500473.2509</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>91935.073</t>
+          <t>22970149887.8511</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>44013.483</t>
+          <t>4325.16680261337</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>44132.228</t>
+          <t>-420.216941257668</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>44957.824</t>
+          <t>-3879.3638897623</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>45465.596</t>
+          <t>-5646.5640924135</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>46879.921</t>
+          <t>-7683.67425728115</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>48498.432</t>
+          <t>-8529.58232138208</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>52739.086</t>
+          <t>-4641.4668773883</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>51798.341</t>
+          <t>-4361.26382598899</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>53539.709</t>
+          <t>-2741.47072423993</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>56243.832</t>
+          <t>-1984.24970427598</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>58621.768</t>
+          <t>2391.71861266029</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>62163.465</t>
+          <t>-290.02538297949</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>65889.368</t>
+          <t>-4496.72926315063</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>68468.894</t>
+          <t>-12039.0826206775</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>69394.773</t>
+          <t>6994.66674394492</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>90003.533</t>
+          <t>5307162137.23319</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>91394.582</t>
+          <t>3429164555.67757</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>89535.309</t>
+          <t>3588906640.75387</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>89322.3</t>
+          <t>1888926875.91466</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>85825.928</t>
+          <t>947641698.651171</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>86590.829</t>
+          <t>79817368.9058416</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>78209.769</t>
+          <t>491237428.598939</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>74845.286</t>
+          <t>-79660791.3547158</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>76377.219</t>
+          <t>799885510.364904</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>79770.075</t>
+          <t>358531216.679094</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>83329.892</t>
+          <t>-121977183.928902</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>87622.269</t>
+          <t>-1105702129.25434</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>93473.531</t>
+          <t>-3067391876.81414</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>93528.83</t>
+          <t>-6548841051.28424</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>87265.671</t>
+          <t>-2426002954.44406</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>66902.07927</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>72393.64547</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>71058.53687</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>76788.56472</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>72655.5947</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>73159.29721</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>78760.74134</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>80203.44746</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>89780.8755</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>107873.44568</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>127833.46508</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>143520.73575</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.577</t>
+          <t>179221.20543</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>222432.85622</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>184289.98954</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>51610.874</t>
+          <t>-0.0758416078262403</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>52218.449</t>
+          <t>-0.0757022375858964</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>52626.032</t>
+          <t>-0.0850823533383653</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>52590.512</t>
+          <t>-0.0950725202021011</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>50914.569</t>
+          <t>-0.103577164804921</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>49672.949</t>
+          <t>-0.0227658275929951</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>45122.535</t>
+          <t>0.00327696236818935</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>43748.203</t>
+          <t>0.0137438063582751</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>44483.476</t>
+          <t>0.020810741731105</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>45617.726</t>
+          <t>0.039911932707189</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>46964.328</t>
+          <t>0.0466037532633269</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>48610.237</t>
+          <t>0.0590318048770405</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>49914.122</t>
+          <t>0.0661443494075685</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>52177.421</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>51789.183</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>55322.2305835788</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>64243.2401122611</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>65817.015680837</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>72614.0086731007</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>69775.9544477548</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>69008.2517646412</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>78158.5883185697</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>77618.7934548832</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>82843.1121536122</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>91917.3966184302</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>108968.128312447</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>121452.55447037</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>151637.307249389</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>199382.989951675</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>158759.834349227</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>17871.136</t>
+          <t>122419.634625984</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>18798.201</t>
+          <t>136365.178028398</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19512.217</t>
+          <t>138702.568470208</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>20064.186</t>
+          <t>158088.637722025</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>18908.856</t>
+          <t>154789.819536808</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>18493.58</t>
+          <t>119603.910053449</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16058.08</t>
+          <t>121330.985757966</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15299.252</t>
+          <t>117856.895027572</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>15066.994</t>
+          <t>123175.866337015</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>14681.148</t>
+          <t>135218.424879093</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>15720.568</t>
+          <t>158798.181727026</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>16079.975</t>
+          <t>171313.241181191</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>16839.022</t>
+          <t>208900.965393392</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>18321.297</t>
+          <t>271054.618660394</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>16872.353</t>
+          <t>216652.208613619</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>146.28</t>
+          <t>426619.898502123</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>134.77</t>
+          <t>464177.552923918</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>130.41</t>
+          <t>452635.807269903</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>126.6</t>
+          <t>494548.346133708</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>147.93</t>
+          <t>480450.148587969</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>162.24</t>
+          <t>486745.455241911</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>228.43</t>
+          <t>539597.482887317</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>238.57</t>
+          <t>553798.994567247</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>255.34</t>
+          <t>601526.101635378</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>283.1</t>
+          <t>671938.500413658</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>272.9</t>
+          <t>785564.806423376</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>286.59</t>
+          <t>855912.421604851</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>291.29</t>
+          <t>1042806.03475039</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>273.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>311.29</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10.632</t>
+          <t>122419.634625984</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.757</t>
+          <t>129436.259353255</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9.692</t>
+          <t>142833.683496869</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9.063</t>
+          <t>160530.459879988</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.427</t>
+          <t>177550.859327161</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>9.004</t>
+          <t>134371.612221007</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>123613.532384102</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>7.227</t>
+          <t>120635.015915468</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6.588</t>
+          <t>119602.990802215</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>112883.529539395</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>5.096</t>
+          <t>117762.490628025</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4.658</t>
+          <t>119156.286087209</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>3.951</t>
+          <t>122537.678036396</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.159</t>
+          <t>135611.742378845</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>134732.675475313</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>55322.2305835788</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>60999.3820175542</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>66319.2242131613</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>70225.6586635871</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>72995.5337176053</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>73378.843003773</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>75466.455410065</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>72914.3072583563</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>73912.6866171794</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>72988.5945707342</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>75529.0483650772</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>80455.9358743324</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>87439.8862806087</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>97107.2575900012</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>93588.395627913</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>220.494934016407</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1668.99448160193</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>584.825569792097</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-4351.11449202529</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-6626.01872680818</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>33012.2346265512</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>48575.428752034</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>57478.7543324281</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>68302.5263629852</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>90591.5509509075</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109261.328442974</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>129047.870718809</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>164364.393956608</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>198544.131219606</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>168885.787786381</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>44013482699.0598</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>44132228299.4231</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>44957823762.591</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>45465596492.6556</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>46879920871.2262</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>48498432380.2937</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>52739085691.84</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>51798341308.2261</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>53539709130.8785</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>56243832235.506</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>58621768007.6028</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>62163464900.5211</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>65889367914.8766</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>68468893855.9118</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>69394772823.5804</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>74042234037.9819</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>75401433194.3399</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>77771290733.7853</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>79554212879.0217</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>79299951508.4066</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>76553058923.776</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>73096046434.3458</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>72086912511.1222</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>73565590846.4519</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>76731214461.6207</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>79042370120.1452</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>82515682039.5835</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>86558884664.5483</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>90237821206.0098</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>91935073217.9423</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>51610873733.2739</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>52218448574.3795</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>52626031885.5784</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>52590511955.8403</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>50914569387.5399</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>49672948586.3702</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>45122535111.1273</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>43748202947.5566</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>44483476296.7141</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>45617726490.6036</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>46964328063.2213</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>48610236641.668</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>49914121522.7158</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>52177420533.9095</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>51789183356.9374</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14735200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>15020600</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>15438700</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>15800400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15375000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>15017500</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14194800</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>13766300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>13606100</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>13773300</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>14074500</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>14529900</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>15174200</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>15783645.889573</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>15786155.3712382</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>8713700</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>8724700</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>8863200</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>8938400</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>8896000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>9354100</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10206600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>9879500</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>9890800</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>10083800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>10436300</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>10962900</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>11604900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>12125800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>12206700</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>28305086293.1525</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>28879294419.0028</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>29662440618.8973</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>30129464561.2833</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>29829817522.3089</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>28892502127.8591</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26456570789.3266</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>25507398965.6909</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>25162379461.1629</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>25538377300.9695</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>25769666149.1946</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>26509432484.7037</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>27585810137.3996</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>28604273526.7837</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>28297149673.6112</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>15014241815.3346</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>15032707867.3007</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>15287944968.716</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15407358482.0686</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>15801550161.6009</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>16365614284.9565</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>17542311839.8331</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>16854514610.4582</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>16906382225.1846</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>17319250893.9937</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>17709690793.7366</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>18612378276.4895</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>19705785159.2337</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>20418936958.2142</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>20070824201.2121</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.197493838927671</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.214380705497248</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.230918530591076</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.232116469535008</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.277251635777324</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.288095700635141</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.295513218664395</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.304555318021329</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.299157843309884</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.319155072994049</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.728913401470213</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.713749162074466</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.704022519621681</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.682689167535268</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.67044334674335</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.662467146601343</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.656010408643502</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.646989663617845</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.649286049704992</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.631515982679652</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0735927596021157</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0718701324282859</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0650589497872431</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0851943629297249</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0523050174793255</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0494371527635151</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0484763726921036</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0484550183608254</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0515561069851239</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0493289443262993</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.245560109621577</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.245560109621577</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.245560109621577</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.245560109621577</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.245560109621577</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.245560109621577</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.265472914298966</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.280188938276081</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.305522940440345</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.337092962442832</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.351700519327732</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.361631061331169</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.368252691901072</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.37426401807909</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.398389880096646</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.715398289341023</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.715398289341023</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.715398289341023</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.715398289341023</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.715398289341023</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.715398289341023</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.696262296160517</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.685409189560786</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.66430498832247</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.636013794438747</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.62332339219328</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.614254002327394</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.607154539584167</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.600660556376035</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.577962927126779</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0390416010374007</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0390416010374007</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0390416010374007</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0390416010374007</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0390416010374007</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0390416010374007</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0382647895405175</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0344018721631333</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.030172071237185</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0268932431184213</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0249760884789873</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0241149363414369</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0245927685147615</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.025075425544875</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0236471927765749</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>264793.69278</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>299043.88961</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>300257.78319</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>329628.38256</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>320451.15519</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>335095.52743</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>374515.27799</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>384060.67339</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>424185.41114</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>509518.75332</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>603836.20512</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>695167.79525</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>883621.63806</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1111403.68187</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>865782.85723</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>122640.12956</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>138034.17251</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>139287.39404</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>153737.52323</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>148163.80081</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>152616.14468</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>169906.41451</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>175335.64936</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>191478.3927</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>225809.97583</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>268059.51017</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>300361.1119</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>373265.35935</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>469598.74988</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>385537.9964</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1034179.94551128</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1062964.04076036</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1105245.96981106</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1156671.62373569</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1210867.2853591</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1263983.15299466</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1302898.57441767</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1332205.72669073</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1359887.13054996</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1391996.40648563</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1428955.21337048</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1479953.99581784</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1549336.65184272</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
